--- a/xls/square_12_tri3_12.xlsx
+++ b/xls/square_12_tri3_12.xlsx
@@ -418,7 +418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -482,13 +482,13 @@
         <v>864</v>
       </c>
       <c r="I12">
-        <v>1.8451051506463694</v>
+        <v>1.8451052534503607</v>
       </c>
       <c r="J12">
-        <v>-1.098837243830051</v>
+        <v>-1.0988371573342712</v>
       </c>
       <c r="K12">
-        <v>0.14668177169628632</v>
+        <v>0.14668189030085457</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -517,13 +517,13 @@
         <v>1014</v>
       </c>
       <c r="I13">
-        <v>-2.1788220488562025</v>
+        <v>-2.1788217127160032</v>
       </c>
       <c r="J13">
-        <v>-1.8329929308908464</v>
+        <v>-1.8329930604006333</v>
       </c>
       <c r="K13">
-        <v>0.7962325089327823</v>
+        <v>0.7962285482068486</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -552,13 +552,13 @@
         <v>1176</v>
       </c>
       <c r="I14">
-        <v>-0.7924645668040169</v>
+        <v>-0.7924645756827977</v>
       </c>
       <c r="J14">
-        <v>-0.6752971786387373</v>
+        <v>-0.6752971734792664</v>
       </c>
       <c r="K14">
-        <v>3.343740847768328</v>
+        <v>3.343740868878064</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -587,13 +587,13 @@
         <v>1350</v>
       </c>
       <c r="I15">
-        <v>-1.1414850356499353</v>
+        <v>-1.1414849136201162</v>
       </c>
       <c r="J15">
-        <v>-1.0618236749714152</v>
+        <v>-1.0618236013689184</v>
       </c>
       <c r="K15">
-        <v>3.3805748060292413</v>
+        <v>3.3805747791110665</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -622,13 +622,13 @@
         <v>1536</v>
       </c>
       <c r="I16">
-        <v>-0.16074276064115453</v>
+        <v>-0.16074275447105693</v>
       </c>
       <c r="J16">
-        <v>-0.14977278427147356</v>
+        <v>-0.14977277865633928</v>
       </c>
       <c r="K16">
-        <v>3.8398572448686172</v>
+        <v>3.8398572362424823</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -657,13 +657,13 @@
         <v>1734</v>
       </c>
       <c r="I17">
-        <v>-0.07937548589262373</v>
+        <v>-0.07937548639516288</v>
       </c>
       <c r="J17">
-        <v>-0.07563732589495908</v>
+        <v>-0.07563732654105944</v>
       </c>
       <c r="K17">
-        <v>3.81682127524622</v>
+        <v>3.8168212793695937</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -692,13 +692,13 @@
         <v>1944</v>
       </c>
       <c r="I18">
-        <v>-0.05736679546539617</v>
+        <v>-0.057366794933307194</v>
       </c>
       <c r="J18">
-        <v>-0.05319443658302504</v>
+        <v>-0.05319443609260063</v>
       </c>
       <c r="K18">
-        <v>3.756294476730599</v>
+        <v>3.7562944729035705</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -727,13 +727,13 @@
         <v>2166</v>
       </c>
       <c r="I19">
-        <v>-0.010388943948067554</v>
+        <v>-0.010388943948768605</v>
       </c>
       <c r="J19">
-        <v>-0.010247361083607803</v>
+        <v>-0.010247361082037963</v>
       </c>
       <c r="K19">
-        <v>3.4444491937629538</v>
+        <v>3.4444491935319808</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -762,13 +762,13 @@
         <v>2400</v>
       </c>
       <c r="I20">
-        <v>-0.005651673613089876</v>
+        <v>-0.005651673609098755</v>
       </c>
       <c r="J20">
-        <v>-0.005639123489312746</v>
+        <v>-0.005639123486345759</v>
       </c>
       <c r="K20">
-        <v>3.3191866717041347</v>
+        <v>3.319186671571755</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -797,13 +797,13 @@
         <v>2646</v>
       </c>
       <c r="I21">
-        <v>-0.004205617378712759</v>
+        <v>-0.0042056173780404115</v>
       </c>
       <c r="J21">
-        <v>-0.0036041982492345027</v>
+        <v>-0.0036041982488690884</v>
       </c>
       <c r="K21">
-        <v>3.2010169411998017</v>
+        <v>3.201016941253622</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -832,13 +832,13 @@
         <v>2904</v>
       </c>
       <c r="I22">
-        <v>-0.004599461388007346</v>
+        <v>-0.004599461387717599</v>
       </c>
       <c r="J22">
-        <v>-0.0043906895467105515</v>
+        <v>-0.004390689546653224</v>
       </c>
       <c r="K22">
-        <v>3.260831938690983</v>
+        <v>3.260831938973461</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -867,13 +867,13 @@
         <v>3174</v>
       </c>
       <c r="I23">
-        <v>0.00011303937467271107</v>
+        <v>0.00011303937464446363</v>
       </c>
       <c r="J23">
-        <v>3.622079643630411e-5</v>
+        <v>3.622079642695091e-5</v>
       </c>
       <c r="K23">
-        <v>2.3055788295371102</v>
+        <v>2.3055788295908934</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -902,13 +902,293 @@
         <v>3456</v>
       </c>
       <c r="I24">
-        <v>-0.0001428839947243661</v>
+        <v>-0.000142883994721231</v>
       </c>
       <c r="J24">
-        <v>-8.329073175297253e-5</v>
+        <v>-8.329073175123641e-5</v>
       </c>
       <c r="K24">
-        <v>2.0254311657030235</v>
+        <v>2.0254311654893153</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25">
+        <v>169</v>
+      </c>
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25">
+        <v>169</v>
+      </c>
+      <c r="E25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25">
+        <v>676</v>
+      </c>
+      <c r="G25" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25">
+        <v>3750</v>
+      </c>
+      <c r="I25">
+        <v>-1.3568445203470004e-7</v>
+      </c>
+      <c r="J25">
+        <v>-1.5152182929106563e-7</v>
+      </c>
+      <c r="K25">
+        <v>1.0775580793272796</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26">
+        <v>169</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26">
+        <v>169</v>
+      </c>
+      <c r="E26" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26">
+        <v>729</v>
+      </c>
+      <c r="G26" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26">
+        <v>4056</v>
+      </c>
+      <c r="I26">
+        <v>-3.3619472757714055e-7</v>
+      </c>
+      <c r="J26">
+        <v>-2.761517602361344e-7</v>
+      </c>
+      <c r="K26">
+        <v>1.1127080354657706</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27">
+        <v>169</v>
+      </c>
+      <c r="C27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27">
+        <v>169</v>
+      </c>
+      <c r="E27" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27">
+        <v>784</v>
+      </c>
+      <c r="G27" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27">
+        <v>4374</v>
+      </c>
+      <c r="I27">
+        <v>-2.5431579255797e-7</v>
+      </c>
+      <c r="J27">
+        <v>-2.0644064256452545e-7</v>
+      </c>
+      <c r="K27">
+        <v>1.0473610205582415</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28">
+        <v>169</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28">
+        <v>169</v>
+      </c>
+      <c r="E28" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28">
+        <v>841</v>
+      </c>
+      <c r="G28" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28">
+        <v>4704</v>
+      </c>
+      <c r="I28">
+        <v>-2.3651479491456418e-7</v>
+      </c>
+      <c r="J28">
+        <v>-1.9577188883752588e-7</v>
+      </c>
+      <c r="K28">
+        <v>1.0418302640309567</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29">
+        <v>169</v>
+      </c>
+      <c r="C29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29">
+        <v>169</v>
+      </c>
+      <c r="E29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29">
+        <v>900</v>
+      </c>
+      <c r="G29" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29">
+        <v>5046</v>
+      </c>
+      <c r="I29">
+        <v>-2.2544799112914303e-7</v>
+      </c>
+      <c r="J29">
+        <v>-1.870510531475169e-7</v>
+      </c>
+      <c r="K29">
+        <v>1.0330505624273214</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30">
+        <v>169</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30">
+        <v>169</v>
+      </c>
+      <c r="E30" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30">
+        <v>961</v>
+      </c>
+      <c r="G30" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30">
+        <v>5400</v>
+      </c>
+      <c r="I30">
+        <v>-2.1748857170145416e-7</v>
+      </c>
+      <c r="J30">
+        <v>-1.8049612501844081e-7</v>
+      </c>
+      <c r="K30">
+        <v>1.0253820165126122</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31">
+        <v>169</v>
+      </c>
+      <c r="C31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31">
+        <v>169</v>
+      </c>
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31">
+        <v>1024</v>
+      </c>
+      <c r="G31" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31">
+        <v>5766</v>
+      </c>
+      <c r="I31">
+        <v>-2.1109606568676378e-7</v>
+      </c>
+      <c r="J31">
+        <v>-1.7508648226600745e-7</v>
+      </c>
+      <c r="K31">
+        <v>1.0183451363245268</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32">
+        <v>169</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32">
+        <v>169</v>
+      </c>
+      <c r="E32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32">
+        <v>1089</v>
+      </c>
+      <c r="G32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32">
+        <v>6144</v>
+      </c>
+      <c r="I32">
+        <v>-2.0636624307398133e-7</v>
+      </c>
+      <c r="J32">
+        <v>-1.7081142857116956e-7</v>
+      </c>
+      <c r="K32">
+        <v>1.0118847643840037</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_12_tri3_12.xlsx
+++ b/xls/square_12_tri3_12.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10">
+        <v>169</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10">
+        <v>169</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10">
+        <v>121</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10">
+        <v>600</v>
+      </c>
+      <c r="I10">
+        <v>7.498119771147776</v>
+      </c>
+      <c r="J10">
+        <v>2.52372863459826</v>
+      </c>
+      <c r="K10">
+        <v>3.0602633485134105</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>169</v>
+      </c>
+      <c r="C11" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11">
+        <v>169</v>
+      </c>
+      <c r="E11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11">
+        <v>144</v>
+      </c>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11">
+        <v>726</v>
+      </c>
+      <c r="I11">
+        <v>4.334504367917372</v>
+      </c>
+      <c r="J11">
+        <v>0.588266162548463</v>
+      </c>
+      <c r="K11">
+        <v>1.5701437777081353</v>
+      </c>
+    </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
         <v>11</v>
